--- a/salidas/empresas/FCX.xlsx
+++ b/salidas/empresas/FCX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>20.51920318603516</v>
+        <v>20.51919555664062</v>
       </c>
       <c r="C2" t="n">
         <v>32.125</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.16944885253906</v>
+        <v>16.1694450378418</v>
       </c>
       <c r="C3" t="n">
         <v>25.31500053405762</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>19.28082847595215</v>
+        <v>19.28082275390625</v>
       </c>
       <c r="C4" t="n">
         <v>29.88500022888184</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93881988525391</v>
+        <v>20.93881607055664</v>
       </c>
       <c r="C5" t="n">
         <v>32.29000091552734</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15367698669434</v>
+        <v>18.15367889404297</v>
       </c>
       <c r="C6" t="n">
         <v>27.9950008392334</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.25408172607422</v>
+        <v>18.25407600402832</v>
       </c>
       <c r="C7" t="n">
         <v>27.70499992370605</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>18.07709312438965</v>
+        <v>18.07708740234375</v>
       </c>
       <c r="C8" t="n">
         <v>27.28000068664551</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.28641700744629</v>
+        <v>19.28642272949219</v>
       </c>
       <c r="C9" t="n">
         <v>29.10499954223633</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>17.89513397216797</v>
+        <v>17.89513778686523</v>
       </c>
       <c r="C10" t="n">
         <v>26.6299991607666</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.44050788879395</v>
+        <v>20.44049453735352</v>
       </c>
       <c r="C11" t="n">
         <v>30.23999977111816</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.24825096130371</v>
+        <v>21.24824523925781</v>
       </c>
       <c r="C12" t="n">
         <v>31.43499946594238</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.0682487487793</v>
+        <v>19.06825065612793</v>
       </c>
       <c r="C13" t="n">
         <v>27.86499977111816</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.75934410095215</v>
+        <v>19.75933837890625</v>
       </c>
       <c r="C15" t="n">
         <v>28.70499992370605</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.78123474121094</v>
+        <v>22.78123092651367</v>
       </c>
       <c r="C16" t="n">
         <v>33.09500122070312</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.21900939941406</v>
+        <v>23.21901512145996</v>
       </c>
       <c r="C17" t="n">
         <v>33.58000183105469</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.63308906555176</v>
+        <v>28.63310623168945</v>
       </c>
       <c r="C19" t="n">
         <v>41.40999984741211</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.60356140136719</v>
+        <v>32.60355377197266</v>
       </c>
       <c r="C20" t="n">
         <v>46.9900016784668</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>30.32775497436523</v>
+        <v>30.32776069641113</v>
       </c>
       <c r="C21" t="n">
         <v>43.70999908447266</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>36.38845062255859</v>
+        <v>36.38845825195312</v>
       </c>
       <c r="C22" t="n">
         <v>52.44499969482422</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>40.93469619750977</v>
+        <v>40.93468856811523</v>
       </c>
       <c r="C23" t="n">
         <v>58.84000015258789</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.41255950927734</v>
+        <v>34.41253662109375</v>
       </c>
       <c r="C24" t="n">
         <v>49.46500015258789</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.03628540039062</v>
+        <v>31.03628349304199</v>
       </c>
       <c r="C26" t="n">
         <v>44.40999984741211</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>39.90696716308594</v>
+        <v>39.90695953369141</v>
       </c>
       <c r="C29" t="n">
         <v>56.875</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>41.11381912231445</v>
+        <v>41.11382675170898</v>
       </c>
       <c r="C31" t="n">
         <v>58.59500122070312</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.08343887329102</v>
+        <v>34.08343505859375</v>
       </c>
       <c r="C32" t="n">
         <v>48.375</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>31.46596908569336</v>
+        <v>31.46596336364746</v>
       </c>
       <c r="C33" t="n">
         <v>44.65999984741211</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.562747001647949</v>
+        <v>8.562749862670898</v>
       </c>
       <c r="C36" t="n">
         <v>11.99499988555908</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>8.723365783691406</v>
+        <v>8.723362922668457</v>
       </c>
       <c r="C37" t="n">
         <v>12.22000026702881</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.973217964172363</v>
+        <v>8.973215103149414</v>
       </c>
       <c r="C38" t="n">
         <v>12.56999969482422</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.60259437561035</v>
+        <v>13.60259532928467</v>
       </c>
       <c r="C40" t="n">
         <v>19.05500030517578</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.22305774688721</v>
+        <v>15.22305965423584</v>
       </c>
       <c r="C41" t="n">
         <v>21.32500076293945</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.42768859863281</v>
+        <v>19.42769050598145</v>
       </c>
       <c r="C42" t="n">
         <v>27.21500015258789</v>
@@ -1267,11 +1279,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.8857536315918</v>
+        <v>17.88576126098633</v>
       </c>
       <c r="C43" t="n">
         <v>25.05500030517578</v>
@@ -1292,11 +1304,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>21.52286911010742</v>
+        <v>21.52287483215332</v>
       </c>
       <c r="C44" t="n">
         <v>30.14999961853027</v>
@@ -1317,11 +1329,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>22.47943878173828</v>
+        <v>22.47944068908691</v>
       </c>
       <c r="C45" t="n">
         <v>31.48999977111816</v>
@@ -1342,7 +1354,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1367,11 +1379,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.18437194824219</v>
+        <v>26.18436622619629</v>
       </c>
       <c r="C47" t="n">
         <v>36.68000030517578</v>
@@ -1392,11 +1404,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.55380439758301</v>
+        <v>29.55379295349121</v>
       </c>
       <c r="C48" t="n">
         <v>41.40000152587891</v>
@@ -1417,11 +1429,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>28.65788650512695</v>
+        <v>28.65789604187012</v>
       </c>
       <c r="C49" t="n">
         <v>40.14500045776367</v>
@@ -1442,11 +1454,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>23.84583854675293</v>
+        <v>23.84585571289062</v>
       </c>
       <c r="C50" t="n">
         <v>33.34500122070312</v>
@@ -1467,11 +1479,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>26.87440490722656</v>
+        <v>26.87439918518066</v>
       </c>
       <c r="C51" t="n">
         <v>37.58000183105469</v>
@@ -1496,11 +1508,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.87076950073242</v>
+        <v>29.87078094482422</v>
       </c>
       <c r="C52" t="n">
         <v>41.77000045776367</v>
@@ -1525,11 +1537,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>27.05478286743164</v>
+        <v>27.0547924041748</v>
       </c>
       <c r="C53" t="n">
         <v>37.76499938964844</v>
@@ -1554,7 +1566,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1583,11 +1595,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.18031311035156</v>
+        <v>21.18031692504883</v>
       </c>
       <c r="C55" t="n">
         <v>29.56500053405762</v>
@@ -1612,11 +1624,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>25.74774742126465</v>
+        <v>25.74774551391602</v>
       </c>
       <c r="C56" t="n">
         <v>35.77000045776367</v>
@@ -1641,11 +1653,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.90970611572266</v>
+        <v>25.90971565246582</v>
       </c>
       <c r="C57" t="n">
         <v>35.99499893188477</v>
@@ -1670,11 +1682,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.73245811462402</v>
+        <v>30.73247337341309</v>
       </c>
       <c r="C58" t="n">
         <v>42.69499969482422</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>34.22315979003906</v>
+        <v>34.22317504882812</v>
       </c>
       <c r="C59" t="n">
         <v>47.39500045776367</v>
@@ -1728,7 +1740,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1757,11 +1769,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>43.74797821044922</v>
+        <v>43.74796676635742</v>
       </c>
       <c r="C61" t="n">
         <v>60.04499816894531</v>
@@ -1786,11 +1798,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>39.78018569946289</v>
+        <v>39.78018188476562</v>
       </c>
       <c r="C62" t="n">
         <v>54.375</v>
@@ -1815,11 +1827,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.73766326904297</v>
+        <v>38.73766708374023</v>
       </c>
       <c r="C63" t="n">
         <v>52.95000076293945</v>
@@ -1844,11 +1856,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>40.63980865478516</v>
+        <v>40.63980102539062</v>
       </c>
       <c r="C64" t="n">
         <v>55.54999923706055</v>
@@ -1873,11 +1885,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>40.4403190612793</v>
+        <v>40.44033432006836</v>
       </c>
       <c r="C65" t="n">
         <v>55.02000045776367</v>
@@ -1902,11 +1914,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.32730484008789</v>
+        <v>38.32731628417969</v>
       </c>
       <c r="C66" t="n">
         <v>51.63999938964844</v>
@@ -1931,11 +1943,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.26248168945312</v>
+        <v>39.26247406005859</v>
       </c>
       <c r="C67" t="n">
         <v>52.90000152587891</v>
@@ -1960,11 +1972,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.48957824707031</v>
+        <v>39.48956298828125</v>
       </c>
       <c r="C68" t="n">
         <v>52.95999908447266</v>
@@ -1989,11 +2001,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.12752914428711</v>
+        <v>35.12751388549805</v>
       </c>
       <c r="C69" t="n">
         <v>47.11000061035156</v>
@@ -2018,11 +2030,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.70501708984375</v>
+        <v>22.70501327514648</v>
       </c>
       <c r="C70" t="n">
         <v>30.45000076293945</v>
@@ -2047,11 +2059,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>30.23302459716797</v>
+        <v>30.23303413391113</v>
       </c>
       <c r="C71" t="n">
         <v>40.2599983215332</v>
@@ -2076,11 +2088,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>29.73740577697754</v>
+        <v>29.73739814758301</v>
       </c>
       <c r="C72" t="n">
         <v>39.59999847412109</v>
@@ -2105,11 +2117,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>27.62725448608398</v>
+        <v>27.62726020812988</v>
       </c>
       <c r="C73" t="n">
         <v>36.79000091552734</v>
@@ -2134,11 +2146,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.91614532470703</v>
+        <v>34.91615295410156</v>
       </c>
       <c r="C74" t="n">
         <v>46.20999908447266</v>
@@ -2163,11 +2175,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>32.15822219848633</v>
+        <v>32.15822982788086</v>
       </c>
       <c r="C75" t="n">
         <v>42.56000137329102</v>
@@ -2192,11 +2204,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.74292755126953</v>
+        <v>28.74292945861816</v>
       </c>
       <c r="C76" t="n">
         <v>38.04000091552734</v>
@@ -2221,11 +2233,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.18879318237305</v>
+        <v>29.18879127502441</v>
       </c>
       <c r="C77" t="n">
         <v>38.29999923706055</v>
@@ -2250,11 +2262,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.4179859161377</v>
+        <v>24.41798973083496</v>
       </c>
       <c r="C78" t="n">
         <v>32.04000091552734</v>
@@ -2279,11 +2291,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.96507263183594</v>
+        <v>25.96506881713867</v>
       </c>
       <c r="C79" t="n">
         <v>34.06999969482422</v>
@@ -2308,11 +2320,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>25.90527153015137</v>
+        <v>25.9052619934082</v>
       </c>
       <c r="C80" t="n">
         <v>33.66999816894531</v>
@@ -2337,11 +2349,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>27.78256988525391</v>
+        <v>27.78257179260254</v>
       </c>
       <c r="C81" t="n">
         <v>36.11000061035156</v>
@@ -2366,7 +2378,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2395,11 +2407,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>30.14839553833008</v>
+        <v>30.14840126037598</v>
       </c>
       <c r="C83" t="n">
         <v>38.88000106811523</v>
@@ -2424,11 +2436,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>30.24919700622559</v>
+        <v>30.24919509887695</v>
       </c>
       <c r="C84" t="n">
         <v>39.0099983215332</v>
@@ -2453,11 +2465,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.51943016052246</v>
+        <v>26.5194149017334</v>
       </c>
       <c r="C85" t="n">
         <v>34.20000076293945</v>
@@ -2482,11 +2494,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>27.57606887817383</v>
+        <v>27.57607650756836</v>
       </c>
       <c r="C86" t="n">
         <v>35.25</v>
@@ -2511,7 +2523,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2540,11 +2552,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.89412498474121</v>
+        <v>25.89412689208984</v>
       </c>
       <c r="C88" t="n">
         <v>33.09999847412109</v>
@@ -2569,11 +2581,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>24.02862739562988</v>
+        <v>24.02862358093262</v>
       </c>
       <c r="C89" t="n">
         <v>30.43000030517578</v>
@@ -2598,7 +2610,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2627,11 +2639,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>22.7887077331543</v>
+        <v>22.78871536254883</v>
       </c>
       <c r="C91" t="n">
         <v>27.61000061035156</v>
@@ -2656,11 +2668,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>23.60945701599121</v>
+        <v>23.60946083068848</v>
       </c>
       <c r="C92" t="n">
         <v>28.28000068664551</v>
@@ -2685,7 +2697,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2714,11 +2726,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.61672210693359</v>
+        <v>27.61672592163086</v>
       </c>
       <c r="C94" t="n">
         <v>33.08000183105469</v>
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>30.98390197753906</v>
+        <v>30.98390960693359</v>
       </c>
       <c r="C95" t="n">
         <v>36.7599983215332</v>
@@ -2772,11 +2784,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.23916244506836</v>
+        <v>29.23916816711426</v>
       </c>
       <c r="C96" t="n">
         <v>34.68999862670898</v>
@@ -2801,11 +2813,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.8099193572998</v>
+        <v>31.80991554260254</v>
       </c>
       <c r="C97" t="n">
         <v>37.7400016784668</v>
@@ -2830,11 +2842,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>27.55587387084961</v>
+        <v>27.55587768554688</v>
       </c>
       <c r="C98" t="n">
         <v>32.40999984741211</v>
@@ -2859,11 +2871,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>27.73443412780762</v>
+        <v>27.73442459106445</v>
       </c>
       <c r="C99" t="n">
         <v>32.61999893188477</v>
@@ -2888,7 +2900,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2946,11 +2958,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>29.22587203979492</v>
+        <v>29.22587394714355</v>
       </c>
       <c r="C102" t="n">
         <v>34.04999923706055</v>
@@ -2975,11 +2987,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.32875633239746</v>
+        <v>31.32876014709473</v>
       </c>
       <c r="C103" t="n">
         <v>36.5</v>
@@ -3004,11 +3016,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.20615768432617</v>
+        <v>32.20615386962891</v>
       </c>
       <c r="C104" t="n">
         <v>37.22000122070312</v>
@@ -3033,11 +3045,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.47064399719238</v>
+        <v>31.47065353393555</v>
       </c>
       <c r="C105" t="n">
         <v>36.36999893188477</v>
@@ -3062,11 +3074,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>28.25177192687988</v>
+        <v>28.25176620483398</v>
       </c>
       <c r="C106" t="n">
         <v>32.65000152587891</v>
@@ -3091,11 +3103,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>24.91120338439941</v>
+        <v>24.91120529174805</v>
       </c>
       <c r="C107" t="n">
         <v>28.5</v>
@@ -3120,7 +3132,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3149,11 +3161,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>20.41844749450684</v>
+        <v>20.4184513092041</v>
       </c>
       <c r="C109" t="n">
         <v>23.36000061035156</v>
@@ -3178,11 +3190,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>14.89532947540283</v>
+        <v>14.89532566070557</v>
       </c>
       <c r="C110" t="n">
         <v>16.80999946594238</v>
@@ -3207,11 +3219,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.16632461547852</v>
+        <v>19.16633033752441</v>
       </c>
       <c r="C111" t="n">
         <v>21.6299991607666</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>16.79158782958984</v>
+        <v>16.79158020019531</v>
       </c>
       <c r="C112" t="n">
         <v>18.95000076293945</v>
@@ -3261,11 +3273,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.67602348327637</v>
+        <v>20.676025390625</v>
       </c>
       <c r="C113" t="n">
         <v>23.27000045776367</v>
@@ -3288,11 +3300,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>17.45955657958984</v>
+        <v>17.45955848693848</v>
       </c>
       <c r="C114" t="n">
         <v>19.64999961853027</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>16.54437446594238</v>
+        <v>16.54437637329102</v>
       </c>
       <c r="C115" t="n">
         <v>18.6200008392334</v>
@@ -3342,11 +3354,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>10.54157829284668</v>
+        <v>10.541579246521</v>
       </c>
       <c r="C116" t="n">
         <v>11.75</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>9.545734405517578</v>
+        <v>9.545736312866211</v>
       </c>
       <c r="C117" t="n">
         <v>10.64000034332275</v>
@@ -3396,11 +3408,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>8.693436622619629</v>
+        <v>8.693438529968262</v>
       </c>
       <c r="C118" t="n">
         <v>9.689999580383301</v>
@@ -3423,11 +3435,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>10.60047912597656</v>
+        <v>10.60047817230225</v>
       </c>
       <c r="C119" t="n">
         <v>11.77000045776367</v>
@@ -3450,11 +3462,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>7.367198467254639</v>
+        <v>7.367199897766113</v>
       </c>
       <c r="C120" t="n">
         <v>8.180000305175781</v>
@@ -3477,7 +3489,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3504,11 +3516,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>4.142924308776855</v>
+        <v>4.142922878265381</v>
       </c>
       <c r="C122" t="n">
         <v>4.599999904632568</v>
@@ -3531,7 +3543,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>9.31257152557373</v>
+        <v>9.312573432922363</v>
       </c>
       <c r="C124" t="n">
         <v>10.34000015258789</v>
@@ -3585,7 +3597,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3612,11 +3624,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>9.979042053222656</v>
+        <v>9.979044914245605</v>
       </c>
       <c r="C126" t="n">
         <v>11.07999992370605</v>
@@ -3639,11 +3651,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>10.03308010101318</v>
+        <v>10.03308296203613</v>
       </c>
       <c r="C127" t="n">
         <v>11.14000034332275</v>
@@ -3666,11 +3678,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>11.6722412109375</v>
+        <v>11.67223930358887</v>
       </c>
       <c r="C128" t="n">
         <v>12.96000003814697</v>
@@ -3693,11 +3705,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>9.267539978027344</v>
+        <v>9.26754093170166</v>
       </c>
       <c r="C129" t="n">
         <v>10.28999996185303</v>
@@ -3720,11 +3732,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>9.780901908874512</v>
+        <v>9.780904769897461</v>
       </c>
       <c r="C130" t="n">
         <v>10.85999965667725</v>
@@ -3747,11 +3759,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>10.06910800933838</v>
+        <v>10.06910705566406</v>
       </c>
       <c r="C131" t="n">
         <v>11.18000030517578</v>
@@ -3774,11 +3786,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>13.82475757598877</v>
+        <v>13.82475852966309</v>
       </c>
       <c r="C132" t="n">
         <v>15.35000038146973</v>
@@ -3801,11 +3813,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>11.8793830871582</v>
+        <v>11.87938213348389</v>
       </c>
       <c r="C133" t="n">
         <v>13.1899995803833</v>
@@ -3828,11 +3840,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>14.99558544158936</v>
+        <v>14.99558639526367</v>
       </c>
       <c r="C134" t="n">
         <v>16.64999961853027</v>
@@ -3855,11 +3867,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>12.06851863861084</v>
+        <v>12.06851577758789</v>
       </c>
       <c r="C135" t="n">
         <v>13.39999961853027</v>
@@ -3882,11 +3894,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>12.03248977661133</v>
+        <v>12.03249359130859</v>
       </c>
       <c r="C136" t="n">
         <v>13.35999965667725</v>
@@ -3909,11 +3921,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>11.48310470581055</v>
+        <v>11.48310661315918</v>
       </c>
       <c r="C137" t="n">
         <v>12.75</v>
@@ -3936,11 +3948,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>10.34830379486084</v>
+        <v>10.34830284118652</v>
       </c>
       <c r="C138" t="n">
         <v>11.48999977111816</v>
@@ -3963,7 +3975,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3990,11 +4002,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>13.16729354858398</v>
+        <v>13.16729259490967</v>
       </c>
       <c r="C140" t="n">
         <v>14.61999988555908</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>13.31139278411865</v>
+        <v>13.3113956451416</v>
       </c>
       <c r="C141" t="n">
         <v>14.77999973297119</v>
@@ -4044,11 +4056,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>12.64492034912109</v>
+        <v>12.64492321014404</v>
       </c>
       <c r="C142" t="n">
         <v>14.03999996185303</v>
@@ -4071,11 +4083,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>12.5908842086792</v>
+        <v>12.59088611602783</v>
       </c>
       <c r="C143" t="n">
         <v>13.97999954223633</v>
@@ -4096,11 +4108,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>12.53684902191162</v>
+        <v>12.5368480682373</v>
       </c>
       <c r="C144" t="n">
         <v>13.92000007629395</v>
@@ -4121,7 +4133,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>17.56239128112793</v>
+        <v>17.56239891052246</v>
       </c>
       <c r="C146" t="n">
         <v>19.5</v>
@@ -4171,11 +4183,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>16.7518196105957</v>
+        <v>16.75182342529297</v>
       </c>
       <c r="C147" t="n">
         <v>18.60000038146973</v>
@@ -4200,11 +4212,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>15.82416439056396</v>
+        <v>15.82417106628418</v>
       </c>
       <c r="C148" t="n">
         <v>17.56999969482422</v>
@@ -4229,11 +4241,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>13.7368688583374</v>
+        <v>13.73686695098877</v>
       </c>
       <c r="C149" t="n">
         <v>15.21000003814697</v>
@@ -4258,11 +4270,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>15.26318836212158</v>
+        <v>15.26318645477295</v>
       </c>
       <c r="C150" t="n">
         <v>16.89999961853027</v>
@@ -4287,7 +4299,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4316,11 +4328,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>14.94484901428223</v>
+        <v>14.94484519958496</v>
       </c>
       <c r="C152" t="n">
         <v>16.5</v>
@@ -4345,11 +4357,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>12.72576427459717</v>
+        <v>12.72576332092285</v>
       </c>
       <c r="C153" t="n">
         <v>14.05000019073486</v>
@@ -4374,7 +4386,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>10.59200000762939</v>
+        <v>10.59199810028076</v>
       </c>
       <c r="C155" t="n">
         <v>11.64999961853027</v>
@@ -4424,11 +4436,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>10.85566139221191</v>
+        <v>10.85566234588623</v>
       </c>
       <c r="C156" t="n">
         <v>11.9399995803833</v>
@@ -4449,11 +4461,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>9.373690605163574</v>
+        <v>9.373693466186523</v>
       </c>
       <c r="C157" t="n">
         <v>10.3100004196167</v>
@@ -4474,11 +4486,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>10.6287202835083</v>
+        <v>10.62872123718262</v>
       </c>
       <c r="C158" t="n">
         <v>11.64000034332275</v>
@@ -4499,11 +4511,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>11.77925491333008</v>
+        <v>11.77925300598145</v>
       </c>
       <c r="C159" t="n">
         <v>12.89999961853027</v>
@@ -4528,11 +4540,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>11.77012062072754</v>
+        <v>11.77012252807617</v>
       </c>
       <c r="C160" t="n">
         <v>12.89000034332275</v>
@@ -4557,11 +4569,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>11.28257942199707</v>
+        <v>11.28257846832275</v>
       </c>
       <c r="C161" t="n">
         <v>12.3100004196167</v>
@@ -4586,11 +4598,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>8.899582862854004</v>
+        <v>8.89958381652832</v>
       </c>
       <c r="C162" t="n">
         <v>9.710000038146973</v>
@@ -4615,11 +4627,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>10.64100360870361</v>
+        <v>10.64099884033203</v>
       </c>
       <c r="C163" t="n">
         <v>11.60999965667725</v>
@@ -4644,11 +4656,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>10.18277740478516</v>
+        <v>10.18277645111084</v>
       </c>
       <c r="C164" t="n">
         <v>11.0600004196167</v>
@@ -4673,11 +4685,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>8.461093902587891</v>
+        <v>8.461092948913574</v>
       </c>
       <c r="C165" t="n">
         <v>9.189999580383301</v>
@@ -4702,11 +4714,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>8.810954093933105</v>
+        <v>8.810951232910156</v>
       </c>
       <c r="C166" t="n">
         <v>9.569999694824219</v>
@@ -4727,7 +4739,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4752,11 +4764,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>10.53619194030762</v>
+        <v>10.5361909866333</v>
       </c>
       <c r="C168" t="n">
         <v>11.38000011444092</v>
@@ -4777,11 +4789,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>12.14717292785645</v>
+        <v>12.14717197418213</v>
       </c>
       <c r="C169" t="n">
         <v>13.11999988555908</v>
@@ -4802,7 +4814,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4827,11 +4839,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>9.255685806274414</v>
+        <v>9.25568675994873</v>
       </c>
       <c r="C171" t="n">
         <v>9.960000038146973</v>
@@ -4854,11 +4866,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>6.272678852081299</v>
+        <v>6.272678375244141</v>
       </c>
       <c r="C172" t="n">
         <v>6.75</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>8.205592155456543</v>
+        <v>8.205591201782227</v>
       </c>
       <c r="C173" t="n">
         <v>8.829999923706055</v>
@@ -4908,11 +4920,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>8.428619384765625</v>
+        <v>8.428621292114258</v>
       </c>
       <c r="C174" t="n">
         <v>9.069999694824219</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>10.75183582305908</v>
+        <v>10.7518367767334</v>
       </c>
       <c r="C175" t="n">
         <v>11.56999969482422</v>
@@ -4962,11 +4974,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>12.00637245178223</v>
+        <v>12.00637340545654</v>
       </c>
       <c r="C176" t="n">
         <v>12.92000007629395</v>
@@ -4989,11 +5001,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>14.50615119934082</v>
+        <v>14.50614929199219</v>
       </c>
       <c r="C177" t="n">
         <v>15.60999965667725</v>
@@ -5016,7 +5028,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5041,11 +5053,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>16.11381530761719</v>
+        <v>16.11380958557129</v>
       </c>
       <c r="C179" t="n">
         <v>17.34000015258789</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>21.73599052429199</v>
+        <v>21.73598861694336</v>
       </c>
       <c r="C180" t="n">
         <v>23.38999938964844</v>
@@ -5091,7 +5103,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5116,11 +5128,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>25.00707626342773</v>
+        <v>25.00708198547363</v>
       </c>
       <c r="C182" t="n">
         <v>26.90999984741211</v>
@@ -5141,11 +5153,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>31.51207733154297</v>
+        <v>31.5120792388916</v>
       </c>
       <c r="C183" t="n">
         <v>33.90999984741211</v>
@@ -5166,11 +5178,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>30.60137939453125</v>
+        <v>30.60137367248535</v>
       </c>
       <c r="C184" t="n">
         <v>32.93000030517578</v>
@@ -5191,11 +5203,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>35.1214485168457</v>
+        <v>35.12145614624023</v>
       </c>
       <c r="C185" t="n">
         <v>37.70999908447266</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>39.78755950927734</v>
+        <v>39.78754806518555</v>
       </c>
       <c r="C186" t="n">
         <v>42.72000122070312</v>
@@ -5243,11 +5255,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>34.56264114379883</v>
+        <v>34.56264495849609</v>
       </c>
       <c r="C187" t="n">
         <v>37.11000061035156</v>
@@ -5270,11 +5282,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>35.55932235717773</v>
+        <v>35.559326171875</v>
       </c>
       <c r="C188" t="n">
         <v>38.09999847412109</v>
@@ -5297,11 +5309,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>33.9633674621582</v>
+        <v>33.96336364746094</v>
       </c>
       <c r="C189" t="n">
         <v>36.38999938964844</v>
@@ -5324,11 +5336,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>30.36075973510742</v>
+        <v>30.36075782775879</v>
       </c>
       <c r="C190" t="n">
         <v>32.52999877929688</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>35.27853012084961</v>
+        <v>35.27854156494141</v>
       </c>
       <c r="C191" t="n">
         <v>37.72000122070312</v>
@@ -5378,7 +5390,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5407,7 +5419,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5436,11 +5448,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>34.92693710327148</v>
+        <v>34.92694091796875</v>
       </c>
       <c r="C194" t="n">
         <v>37.22000122070312</v>
@@ -5465,11 +5477,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>44.05748748779297</v>
+        <v>44.05747985839844</v>
       </c>
       <c r="C195" t="n">
         <v>46.95000076293945</v>
@@ -5494,11 +5506,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>46.67560577392578</v>
+        <v>46.67559432983398</v>
       </c>
       <c r="C196" t="n">
         <v>49.7400016784668</v>
@@ -5523,11 +5535,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.17106246948242</v>
+        <v>38.17107009887695</v>
       </c>
       <c r="C197" t="n">
         <v>40.54999923706055</v>
@@ -5552,7 +5564,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5581,11 +5593,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54341506958008</v>
+        <v>27.54341125488281</v>
       </c>
       <c r="C199" t="n">
         <v>29.26000022888184</v>
@@ -5610,11 +5622,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>29.86851501464844</v>
+        <v>29.86851119995117</v>
       </c>
       <c r="C200" t="n">
         <v>31.54999923706055</v>
@@ -5639,11 +5651,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>28.02244186401367</v>
+        <v>28.02243995666504</v>
       </c>
       <c r="C201" t="n">
         <v>29.60000038146973</v>
@@ -5668,11 +5680,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>25.87342262268066</v>
+        <v>25.87342643737793</v>
       </c>
       <c r="C202" t="n">
         <v>27.32999992370605</v>
@@ -5697,11 +5709,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>30.15790939331055</v>
+        <v>30.15790748596191</v>
       </c>
       <c r="C203" t="n">
         <v>31.69000053405762</v>
@@ -5726,11 +5738,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>37.87582015991211</v>
+        <v>37.87581253051758</v>
       </c>
       <c r="C204" t="n">
         <v>39.79999923706055</v>
@@ -5755,11 +5767,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.16284561157227</v>
+        <v>36.162841796875</v>
       </c>
       <c r="C205" t="n">
         <v>38</v>
@@ -5784,7 +5796,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5813,11 +5825,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.11873245239258</v>
+        <v>39.11872863769531</v>
       </c>
       <c r="C207" t="n">
         <v>40.97000122070312</v>
@@ -5842,11 +5854,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>39.06143951416016</v>
+        <v>39.06143569946289</v>
       </c>
       <c r="C208" t="n">
         <v>40.90999984741211</v>
@@ -5871,11 +5883,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>36.32952880859375</v>
+        <v>36.32951354980469</v>
       </c>
       <c r="C209" t="n">
         <v>37.90999984741211</v>
@@ -5900,11 +5912,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>32.90836334228516</v>
+        <v>32.90835952758789</v>
       </c>
       <c r="C210" t="n">
         <v>34.34000015258789</v>
@@ -5929,7 +5941,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5958,11 +5970,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.94673919677734</v>
+        <v>42.94673538208008</v>
       </c>
       <c r="C212" t="n">
         <v>44.65000152587891</v>
@@ -5987,7 +5999,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6016,11 +6028,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>35.86748886108398</v>
+        <v>35.86749649047852</v>
       </c>
       <c r="C214" t="n">
         <v>37.29000091552734</v>
@@ -6045,11 +6057,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>32.62311553955078</v>
+        <v>32.62311935424805</v>
       </c>
       <c r="C215" t="n">
         <v>33.77999877929688</v>
@@ -6074,11 +6086,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>36.04187393188477</v>
+        <v>36.04187774658203</v>
       </c>
       <c r="C216" t="n">
         <v>37.31999969482422</v>
@@ -6103,11 +6115,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>41.11207962036133</v>
+        <v>41.1120719909668</v>
       </c>
       <c r="C217" t="n">
         <v>42.56999969482422</v>
@@ -6132,7 +6144,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6161,11 +6173,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>36.64819717407227</v>
+        <v>36.64818954467773</v>
       </c>
       <c r="C219" t="n">
         <v>37.81000137329102</v>
@@ -6190,7 +6202,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6219,11 +6231,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>48.54899978637695</v>
+        <v>48.54899597167969</v>
       </c>
       <c r="C221" t="n">
         <v>49.93999862670898</v>
@@ -6248,11 +6260,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>51.26129531860352</v>
+        <v>51.26128768920898</v>
       </c>
       <c r="C222" t="n">
         <v>52.72999954223633</v>
@@ -6277,7 +6289,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6306,7 +6318,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6335,7 +6347,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6364,11 +6376,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>48.67192840576172</v>
+        <v>48.67192459106445</v>
       </c>
       <c r="C226" t="n">
         <v>49.91999816894531</v>
@@ -6393,11 +6405,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>44.02960586547852</v>
+        <v>44.02960205078125</v>
       </c>
       <c r="C227" t="n">
         <v>45.02000045776367</v>
@@ -6422,11 +6434,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>43.2276496887207</v>
+        <v>43.22765350341797</v>
       </c>
       <c r="C228" t="n">
         <v>44.20000076293945</v>
@@ -6451,11 +6463,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>37.24227905273438</v>
+        <v>37.24228286743164</v>
       </c>
       <c r="C229" t="n">
         <v>38.08000183105469</v>
@@ -6480,11 +6492,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>35.19499206542969</v>
+        <v>35.19498825073242</v>
       </c>
       <c r="C230" t="n">
         <v>35.84999847412109</v>
@@ -6509,11 +6521,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>36.23561859130859</v>
+        <v>36.23562240600586</v>
       </c>
       <c r="C231" t="n">
         <v>36.90999984741211</v>
@@ -6538,7 +6550,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6567,7 +6579,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6596,11 +6608,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>37.94557952880859</v>
+        <v>37.94558334350586</v>
       </c>
       <c r="C234" t="n">
         <v>38.47999954223633</v>
@@ -6625,11 +6637,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>42.74795150756836</v>
+        <v>42.74794769287109</v>
       </c>
       <c r="C235" t="n">
         <v>43.34999847412109</v>
@@ -6654,7 +6666,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6683,7 +6695,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6712,7 +6724,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6741,7 +6753,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6770,7 +6782,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6799,7 +6811,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6828,7 +6840,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6857,7 +6869,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6886,7 +6898,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6915,7 +6927,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6944,7 +6956,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6973,7 +6985,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7002,7 +7014,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7060,32 +7072,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>72.58000183105469</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C250" t="n">
-        <v>72.58000183105469</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="D250" t="n">
-        <v>186533400</v>
+        <v>195674300</v>
       </c>
       <c r="E250" t="n">
         <v>2.04</v>
       </c>
       <c r="F250" t="n">
-        <v>35.57843227012484</v>
+        <v>35.33333423090916</v>
       </c>
       <c r="G250" t="n">
         <v>1436017523</v>
       </c>
       <c r="H250" t="n">
-        <v>104226154448.7666</v>
+        <v>103508145687.2666</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1298963257845984</v>
+        <v>0.1362617773571556</v>
       </c>
     </row>
   </sheetData>
@@ -7117,75 +7129,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39944</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7221,13 +7233,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7263,13 +7275,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7338,7 +7350,7 @@
       <c r="I5" t="n">
         <v>-14.86</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K5" t="n">
@@ -7351,13 +7363,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>39944</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7384,7 +7396,7 @@
       <c r="I6" t="n">
         <v>-16.125</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K6" t="n">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7430,7 +7442,7 @@
       <c r="I7" t="n">
         <v>-16.56</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K7" t="n">
@@ -7443,13 +7455,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7476,7 +7488,7 @@
       <c r="I8" t="n">
         <v>-16.18</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K8" t="n">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I9" t="n">
         <v>2.93</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K9" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I10" t="n">
         <v>3.875</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="K10" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I11" t="n">
         <v>3.885</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="K11" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I12" t="n">
         <v>4.095000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="K12" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I13" t="n">
         <v>4.575</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K13" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I14" t="n">
         <v>5.145</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K14" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I15" t="n">
         <v>5.875</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K15" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I16" t="n">
         <v>5.73</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K16" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I17" t="n">
         <v>4.77</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K17" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K18" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I19" t="n">
         <v>3.31</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K19" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I20" t="n">
         <v>3.07</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K20" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I21" t="n">
         <v>3.18</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K21" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I22" t="n">
         <v>3.06</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="K22" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I23" t="n">
         <v>2.81</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="K23" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I24" t="n">
         <v>2.74</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K24" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I25" t="n">
         <v>2.64</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K25" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I26" t="n">
         <v>2.45</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="K26" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I27" t="n">
         <v>2.42</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="K27" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I28" t="n">
         <v>2.16</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K28" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I29" t="n">
         <v>-1.27</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K29" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I30" t="n">
         <v>-4.14</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K30" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42226</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I31" t="n">
         <v>-6.38</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42226</v>
       </c>
       <c r="K31" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I32" t="n">
         <v>-10.49</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K32" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I33" t="n">
         <v>-11.21</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K33" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I34" t="n">
         <v>-12.18</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K34" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I35" t="n">
         <v>-10.78</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K35" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I36" t="n">
         <v>-7.04</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="K36" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I37" t="n">
         <v>-3.36</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K37" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I38" t="n">
         <v>0.15</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K38" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I39" t="n">
         <v>0.71</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K39" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I40" t="n">
         <v>0.74</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K40" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I41" t="n">
         <v>1.24</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K41" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I42" t="n">
         <v>1.55</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K42" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I43" t="n">
         <v>1.96</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K43" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I44" t="n">
         <v>2.15</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K44" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I45" t="n">
         <v>1.77</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K45" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I46" t="n">
         <v>1.32</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K46" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I47" t="n">
         <v>0.68</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K47" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I48" t="n">
         <v>0.15</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K48" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I49" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K49" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I50" t="n">
         <v>-0.54</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K50" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I51" t="n">
         <v>-0.46</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K51" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I52" t="n">
         <v>-0.08999999999999997</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K52" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I53" t="n">
         <v>0.41</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K53" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I54" t="n">
         <v>1.23</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K54" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I55" t="n">
         <v>1.93</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K55" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I56" t="n">
         <v>2.65</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K56" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I57" t="n">
         <v>2.9</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="K57" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I58" t="n">
         <v>3.46</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K58" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I59" t="n">
         <v>3.3</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K59" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I60" t="n">
         <v>2.64</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K60" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I61" t="n">
         <v>2.39</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="K61" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I62" t="n">
         <v>1.81</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K62" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I63" t="n">
         <v>1.47</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K63" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I64" t="n">
         <v>1.5</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K64" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I65" t="n">
         <v>1.28</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K65" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I66" t="n">
         <v>1.14</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K66" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I67" t="n">
         <v>1.33</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K67" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I68" t="n">
         <v>1.38</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="K68" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I69" t="n">
         <v>1.3</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K69" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I70" t="n">
         <v>1.22</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="K70" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I71" t="n">
         <v>1.33</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="K71" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I72" t="n">
         <v>1.43</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K72" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I73" t="n">
         <v>1.52</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K73" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I74" t="n">
         <v>1.89</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="K74" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I75" t="n">
         <v>2.04</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K75" t="n">
@@ -10595,52 +10607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39944</v>
       </c>
       <c r="C2" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C3" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C4" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C5" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C6" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C7" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C8" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C9" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C10" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C11" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C12" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C13" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C14" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C15" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C16" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C17" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="C18" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="C19" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C20" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C21" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="C22" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="C23" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C24" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42055</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C25" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C26" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42226</v>
       </c>
       <c r="C27" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C28" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42419</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C29" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C30" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C31" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="C32" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42781</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C33" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C34" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C35" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C36" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C37" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C38" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C39" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="C40" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C41" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="C42" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C43" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C44" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C45" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C46" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="C47" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C48" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="C49" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C50" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C51" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C52" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="C53" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C54" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C55" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C56" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="C57" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C58" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C59" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C60" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C61" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C62" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C63" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="C64" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C65" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="C66" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="C67" t="n">
@@ -12749,10 +12761,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C68" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C69" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="C70" t="n">
@@ -12845,10 +12857,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C71" t="n">
@@ -12895,12 +12907,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/FCX.xlsx
+++ b/salidas/empresas/FCX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>20.51919555664062</v>
+        <v>20.51919174194336</v>
       </c>
       <c r="C2" t="n">
         <v>32.125</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1694450378418</v>
+        <v>16.16944122314453</v>
       </c>
       <c r="C3" t="n">
         <v>25.31500053405762</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>19.28082275390625</v>
+        <v>19.28083038330078</v>
       </c>
       <c r="C4" t="n">
         <v>29.88500022888184</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93881607055664</v>
+        <v>20.93882179260254</v>
       </c>
       <c r="C5" t="n">
         <v>32.29000091552734</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15367889404297</v>
+        <v>18.1536750793457</v>
       </c>
       <c r="C6" t="n">
         <v>27.9950008392334</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.25407600402832</v>
+        <v>18.25408172607422</v>
       </c>
       <c r="C7" t="n">
         <v>27.70499992370605</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.28642272949219</v>
+        <v>19.28642082214355</v>
       </c>
       <c r="C9" t="n">
         <v>29.10499954223633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.44049453735352</v>
+        <v>20.44050788879395</v>
       </c>
       <c r="C11" t="n">
         <v>30.23999977111816</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.24824523925781</v>
+        <v>21.24825477600098</v>
       </c>
       <c r="C12" t="n">
         <v>31.43499946594238</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.06825065612793</v>
+        <v>19.0682487487793</v>
       </c>
       <c r="C13" t="n">
         <v>27.86499977111816</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.75933837890625</v>
+        <v>19.75933647155762</v>
       </c>
       <c r="C15" t="n">
         <v>28.70499992370605</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.78123092651367</v>
+        <v>22.78124046325684</v>
       </c>
       <c r="C16" t="n">
         <v>33.09500122070312</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.21901512145996</v>
+        <v>23.21902275085449</v>
       </c>
       <c r="C17" t="n">
         <v>33.58000183105469</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.20870780944824</v>
+        <v>27.20870590209961</v>
       </c>
       <c r="C18" t="n">
         <v>39.34999847412109</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.63310623168945</v>
+        <v>28.63311004638672</v>
       </c>
       <c r="C19" t="n">
         <v>41.40999984741211</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>30.32776069641113</v>
+        <v>30.32775497436523</v>
       </c>
       <c r="C21" t="n">
         <v>43.70999908447266</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>36.38845825195312</v>
+        <v>36.38844680786133</v>
       </c>
       <c r="C22" t="n">
         <v>52.44499969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>40.93468856811523</v>
+        <v>40.93469619750977</v>
       </c>
       <c r="C23" t="n">
         <v>58.84000015258789</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.41253662109375</v>
+        <v>34.41254806518555</v>
       </c>
       <c r="C24" t="n">
         <v>49.46500015258789</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.03628349304199</v>
+        <v>31.03629875183105</v>
       </c>
       <c r="C26" t="n">
         <v>44.40999984741211</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>35.24341201782227</v>
+        <v>35.2434196472168</v>
       </c>
       <c r="C27" t="n">
         <v>50.43000030517578</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>39.90695953369141</v>
+        <v>39.9069709777832</v>
       </c>
       <c r="C29" t="n">
         <v>56.875</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>40.5945930480957</v>
+        <v>40.59458923339844</v>
       </c>
       <c r="C30" t="n">
         <v>57.85499954223633</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>41.11382675170898</v>
+        <v>41.11381530761719</v>
       </c>
       <c r="C31" t="n">
         <v>58.59500122070312</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.08343505859375</v>
+        <v>34.08344268798828</v>
       </c>
       <c r="C32" t="n">
         <v>48.375</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>31.46596336364746</v>
+        <v>31.46596717834473</v>
       </c>
       <c r="C33" t="n">
         <v>44.65999984741211</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>20.02731704711914</v>
+        <v>20.02732086181641</v>
       </c>
       <c r="C34" t="n">
         <v>28.42499923706055</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>10.37238025665283</v>
+        <v>10.37238121032715</v>
       </c>
       <c r="C35" t="n">
         <v>14.52999973297119</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.562749862670898</v>
+        <v>8.562750816345215</v>
       </c>
       <c r="C36" t="n">
         <v>11.99499988555908</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>8.723362922668457</v>
+        <v>8.723365783691406</v>
       </c>
       <c r="C37" t="n">
         <v>12.22000026702881</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.973215103149414</v>
+        <v>8.97321891784668</v>
       </c>
       <c r="C38" t="n">
         <v>12.56999969482422</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.85780715942383</v>
+        <v>10.85781002044678</v>
       </c>
       <c r="C39" t="n">
         <v>15.21000003814697</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.60259532928467</v>
+        <v>13.6025972366333</v>
       </c>
       <c r="C40" t="n">
         <v>19.05500030517578</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.22305965423584</v>
+        <v>15.22306060791016</v>
       </c>
       <c r="C41" t="n">
         <v>21.32500076293945</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.42769050598145</v>
+        <v>19.42769622802734</v>
       </c>
       <c r="C42" t="n">
         <v>27.21500015258789</v>
@@ -1283,7 +1283,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.88576126098633</v>
+        <v>17.8857536315918</v>
       </c>
       <c r="C43" t="n">
         <v>25.05500030517578</v>
@@ -1308,7 +1308,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>21.52287483215332</v>
+        <v>21.52286720275879</v>
       </c>
       <c r="C44" t="n">
         <v>30.14999961853027</v>
@@ -1333,7 +1333,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>22.47944068908691</v>
+        <v>22.47943496704102</v>
       </c>
       <c r="C45" t="n">
         <v>31.48999977111816</v>
@@ -1358,7 +1358,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>24.48895645141602</v>
+        <v>24.48895454406738</v>
       </c>
       <c r="C46" t="n">
         <v>34.30500030517578</v>
@@ -1383,7 +1383,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.18436622619629</v>
+        <v>26.18437576293945</v>
       </c>
       <c r="C47" t="n">
         <v>36.68000030517578</v>
@@ -1408,7 +1408,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.55379295349121</v>
+        <v>29.55378532409668</v>
       </c>
       <c r="C48" t="n">
         <v>41.40000152587891</v>
@@ -1433,7 +1433,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>28.65789604187012</v>
+        <v>28.65790748596191</v>
       </c>
       <c r="C49" t="n">
         <v>40.14500045776367</v>
@@ -1458,7 +1458,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>23.84585571289062</v>
+        <v>23.84584999084473</v>
       </c>
       <c r="C50" t="n">
         <v>33.34500122070312</v>
@@ -1483,7 +1483,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>26.87439918518066</v>
+        <v>26.8744010925293</v>
       </c>
       <c r="C51" t="n">
         <v>37.58000183105469</v>
@@ -1512,7 +1512,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.87078094482422</v>
+        <v>29.87077903747559</v>
       </c>
       <c r="C52" t="n">
         <v>41.77000045776367</v>
@@ -1541,7 +1541,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>27.0547924041748</v>
+        <v>27.05478668212891</v>
       </c>
       <c r="C53" t="n">
         <v>37.76499938964844</v>
@@ -1570,7 +1570,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>25.09185600280762</v>
+        <v>25.09186172485352</v>
       </c>
       <c r="C54" t="n">
         <v>35.02500152587891</v>
@@ -1628,7 +1628,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>25.74774551391602</v>
+        <v>25.74774932861328</v>
       </c>
       <c r="C56" t="n">
         <v>35.77000045776367</v>
@@ -1657,7 +1657,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.90971565246582</v>
+        <v>25.90971183776855</v>
       </c>
       <c r="C57" t="n">
         <v>35.99499893188477</v>
@@ -1686,7 +1686,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.73247337341309</v>
+        <v>30.73246192932129</v>
       </c>
       <c r="C58" t="n">
         <v>42.69499969482422</v>
@@ -1715,7 +1715,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>34.22317504882812</v>
+        <v>34.22317886352539</v>
       </c>
       <c r="C59" t="n">
         <v>47.39500045776367</v>
@@ -1744,7 +1744,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>36.58076858520508</v>
+        <v>36.58078765869141</v>
       </c>
       <c r="C60" t="n">
         <v>50.65999984741211</v>
@@ -1773,7 +1773,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>43.74796676635742</v>
+        <v>43.74797058105469</v>
       </c>
       <c r="C61" t="n">
         <v>60.04499816894531</v>
@@ -1802,7 +1802,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>39.78018188476562</v>
+        <v>39.78017807006836</v>
       </c>
       <c r="C62" t="n">
         <v>54.375</v>
@@ -1831,7 +1831,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.73766708374023</v>
+        <v>38.73766326904297</v>
       </c>
       <c r="C63" t="n">
         <v>52.95000076293945</v>
@@ -1860,7 +1860,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>40.63980102539062</v>
+        <v>40.63981246948242</v>
       </c>
       <c r="C64" t="n">
         <v>55.54999923706055</v>
@@ -1889,7 +1889,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>40.44033432006836</v>
+        <v>40.44032287597656</v>
       </c>
       <c r="C65" t="n">
         <v>55.02000045776367</v>
@@ -1918,7 +1918,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.32731628417969</v>
+        <v>38.32730484008789</v>
       </c>
       <c r="C66" t="n">
         <v>51.63999938964844</v>
@@ -1947,7 +1947,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.26247406005859</v>
+        <v>39.26248550415039</v>
       </c>
       <c r="C67" t="n">
         <v>52.90000152587891</v>
@@ -1976,7 +1976,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.48956298828125</v>
+        <v>39.48955917358398</v>
       </c>
       <c r="C68" t="n">
         <v>52.95999908447266</v>
@@ -2005,7 +2005,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.12751388549805</v>
+        <v>35.12752532958984</v>
       </c>
       <c r="C69" t="n">
         <v>47.11000061035156</v>
@@ -2034,7 +2034,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.70501327514648</v>
+        <v>22.70501136779785</v>
       </c>
       <c r="C70" t="n">
         <v>30.45000076293945</v>
@@ -2063,7 +2063,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>30.23303413391113</v>
+        <v>30.23301696777344</v>
       </c>
       <c r="C71" t="n">
         <v>40.2599983215332</v>
@@ -2092,7 +2092,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>29.73739814758301</v>
+        <v>29.73741340637207</v>
       </c>
       <c r="C72" t="n">
         <v>39.59999847412109</v>
@@ -2121,7 +2121,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>27.62726020812988</v>
+        <v>27.62726211547852</v>
       </c>
       <c r="C73" t="n">
         <v>36.79000091552734</v>
@@ -2150,7 +2150,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.91615295410156</v>
+        <v>34.91615676879883</v>
       </c>
       <c r="C74" t="n">
         <v>46.20999908447266</v>
@@ -2179,7 +2179,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>32.15822982788086</v>
+        <v>32.15822601318359</v>
       </c>
       <c r="C75" t="n">
         <v>42.56000137329102</v>
@@ -2208,7 +2208,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.74292945861816</v>
+        <v>28.74292182922363</v>
       </c>
       <c r="C76" t="n">
         <v>38.04000091552734</v>
@@ -2237,7 +2237,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.18879127502441</v>
+        <v>29.18879508972168</v>
       </c>
       <c r="C77" t="n">
         <v>38.29999923706055</v>
@@ -2266,7 +2266,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.41798973083496</v>
+        <v>24.41799354553223</v>
       </c>
       <c r="C78" t="n">
         <v>32.04000091552734</v>
@@ -2295,7 +2295,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.96506881713867</v>
+        <v>25.96507835388184</v>
       </c>
       <c r="C79" t="n">
         <v>34.06999969482422</v>
@@ -2324,7 +2324,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>25.9052619934082</v>
+        <v>25.9052791595459</v>
       </c>
       <c r="C80" t="n">
         <v>33.66999816894531</v>
@@ -2382,7 +2382,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>30.45234107971191</v>
+        <v>30.45234870910645</v>
       </c>
       <c r="C82" t="n">
         <v>39.58000183105469</v>
@@ -2411,7 +2411,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>30.14840126037598</v>
+        <v>30.14839935302734</v>
       </c>
       <c r="C83" t="n">
         <v>38.88000106811523</v>
@@ -2440,7 +2440,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>30.24919509887695</v>
+        <v>30.24920082092285</v>
       </c>
       <c r="C84" t="n">
         <v>39.0099983215332</v>
@@ -2469,7 +2469,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.5194149017334</v>
+        <v>26.51942825317383</v>
       </c>
       <c r="C85" t="n">
         <v>34.20000076293945</v>
@@ -2498,7 +2498,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>27.57607650756836</v>
+        <v>27.57606506347656</v>
       </c>
       <c r="C86" t="n">
         <v>35.25</v>
@@ -2527,7 +2527,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>24.97101211547852</v>
+        <v>24.97101402282715</v>
       </c>
       <c r="C87" t="n">
         <v>31.92000007629395</v>
@@ -2556,7 +2556,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.89412689208984</v>
+        <v>25.89412879943848</v>
       </c>
       <c r="C88" t="n">
         <v>33.09999847412109</v>
@@ -2585,7 +2585,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>24.02862358093262</v>
+        <v>24.02862548828125</v>
       </c>
       <c r="C89" t="n">
         <v>30.43000030517578</v>
@@ -2614,7 +2614,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.51819801330566</v>
+        <v>24.51820182800293</v>
       </c>
       <c r="C90" t="n">
         <v>31.04999923706055</v>
@@ -2643,7 +2643,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>22.78871536254883</v>
+        <v>22.78871154785156</v>
       </c>
       <c r="C91" t="n">
         <v>27.61000061035156</v>
@@ -2672,7 +2672,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>23.60946083068848</v>
+        <v>23.60945892333984</v>
       </c>
       <c r="C92" t="n">
         <v>28.28000068664551</v>
@@ -2701,7 +2701,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>25.22905731201172</v>
+        <v>25.22905921936035</v>
       </c>
       <c r="C93" t="n">
         <v>30.21999931335449</v>
@@ -2730,7 +2730,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.61672592163086</v>
+        <v>27.61671829223633</v>
       </c>
       <c r="C94" t="n">
         <v>33.08000183105469</v>
@@ -2759,7 +2759,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>30.98390960693359</v>
+        <v>30.98391723632812</v>
       </c>
       <c r="C95" t="n">
         <v>36.7599983215332</v>
@@ -2788,7 +2788,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.23916816711426</v>
+        <v>29.23916435241699</v>
       </c>
       <c r="C96" t="n">
         <v>34.68999862670898</v>
@@ -2817,7 +2817,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.80991554260254</v>
+        <v>31.8099193572998</v>
       </c>
       <c r="C97" t="n">
         <v>37.7400016784668</v>
@@ -2846,7 +2846,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>27.55587768554688</v>
+        <v>27.55587959289551</v>
       </c>
       <c r="C98" t="n">
         <v>32.40999984741211</v>
@@ -2875,7 +2875,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>27.73442459106445</v>
+        <v>27.73442268371582</v>
       </c>
       <c r="C99" t="n">
         <v>32.61999893188477</v>
@@ -2904,7 +2904,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.11702728271484</v>
+        <v>28.11703491210938</v>
       </c>
       <c r="C100" t="n">
         <v>33.06999969482422</v>
@@ -2933,7 +2933,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>29.50052452087402</v>
+        <v>29.50052833557129</v>
       </c>
       <c r="C101" t="n">
         <v>34.36999893188477</v>
@@ -2962,7 +2962,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>29.22587394714355</v>
+        <v>29.22586441040039</v>
       </c>
       <c r="C102" t="n">
         <v>34.04999923706055</v>
@@ -2991,7 +2991,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.32876014709473</v>
+        <v>31.32875633239746</v>
       </c>
       <c r="C103" t="n">
         <v>36.5</v>
@@ -3020,7 +3020,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.20615386962891</v>
+        <v>32.20614624023438</v>
       </c>
       <c r="C104" t="n">
         <v>37.22000122070312</v>
@@ -3049,7 +3049,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>31.47065353393555</v>
+        <v>31.47066307067871</v>
       </c>
       <c r="C105" t="n">
         <v>36.36999893188477</v>
@@ -3078,7 +3078,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>28.25176620483398</v>
+        <v>28.25178146362305</v>
       </c>
       <c r="C106" t="n">
         <v>32.65000152587891</v>
@@ -3107,7 +3107,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>24.91120529174805</v>
+        <v>24.91120147705078</v>
       </c>
       <c r="C107" t="n">
         <v>28.5</v>
@@ -3136,7 +3136,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.46897315979004</v>
+        <v>23.46897125244141</v>
       </c>
       <c r="C108" t="n">
         <v>26.85000038146973</v>
@@ -3194,7 +3194,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>14.89532566070557</v>
+        <v>14.89533042907715</v>
       </c>
       <c r="C110" t="n">
         <v>16.80999946594238</v>
@@ -3223,7 +3223,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.16633033752441</v>
+        <v>19.16632843017578</v>
       </c>
       <c r="C111" t="n">
         <v>21.6299991607666</v>
@@ -3250,7 +3250,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>16.79158020019531</v>
+        <v>16.79158592224121</v>
       </c>
       <c r="C112" t="n">
         <v>18.95000076293945</v>
@@ -3277,7 +3277,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.676025390625</v>
+        <v>20.67602348327637</v>
       </c>
       <c r="C113" t="n">
         <v>23.27000045776367</v>
@@ -3304,7 +3304,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>17.45955848693848</v>
+        <v>17.45955276489258</v>
       </c>
       <c r="C114" t="n">
         <v>19.64999961853027</v>
@@ -3331,7 +3331,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>16.54437637329102</v>
+        <v>16.54436683654785</v>
       </c>
       <c r="C115" t="n">
         <v>18.6200008392334</v>
@@ -3358,7 +3358,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>10.541579246521</v>
+        <v>10.54157638549805</v>
       </c>
       <c r="C116" t="n">
         <v>11.75</v>
@@ -3385,7 +3385,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>9.545736312866211</v>
+        <v>9.545737266540527</v>
       </c>
       <c r="C117" t="n">
         <v>10.64000034332275</v>
@@ -3412,7 +3412,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>8.693438529968262</v>
+        <v>8.693437576293945</v>
       </c>
       <c r="C118" t="n">
         <v>9.689999580383301</v>
@@ -3439,7 +3439,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>10.60047817230225</v>
+        <v>10.6004810333252</v>
       </c>
       <c r="C119" t="n">
         <v>11.77000045776367</v>
@@ -3466,7 +3466,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>7.367199897766113</v>
+        <v>7.36720085144043</v>
       </c>
       <c r="C120" t="n">
         <v>8.180000305175781</v>
@@ -3493,7 +3493,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>6.09730339050293</v>
+        <v>6.097302436828613</v>
       </c>
       <c r="C121" t="n">
         <v>6.769999980926514</v>
@@ -3520,7 +3520,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>4.142922878265381</v>
+        <v>4.142923831939697</v>
       </c>
       <c r="C122" t="n">
         <v>4.599999904632568</v>
@@ -3547,7 +3547,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>6.87185001373291</v>
+        <v>6.871849536895752</v>
       </c>
       <c r="C123" t="n">
         <v>7.630000114440918</v>
@@ -3574,7 +3574,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>9.312573432922363</v>
+        <v>9.31257438659668</v>
       </c>
       <c r="C124" t="n">
         <v>10.34000015258789</v>
@@ -3601,7 +3601,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>12.6088981628418</v>
+        <v>12.60890007019043</v>
       </c>
       <c r="C125" t="n">
         <v>14</v>
@@ -3628,7 +3628,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>9.979044914245605</v>
+        <v>9.979043960571289</v>
       </c>
       <c r="C126" t="n">
         <v>11.07999992370605</v>
@@ -3709,7 +3709,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>9.26754093170166</v>
+        <v>9.267539978027344</v>
       </c>
       <c r="C129" t="n">
         <v>10.28999996185303</v>
@@ -3763,7 +3763,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>10.06910705566406</v>
+        <v>10.06910419464111</v>
       </c>
       <c r="C131" t="n">
         <v>11.18000030517578</v>
@@ -3790,7 +3790,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>13.82475852966309</v>
+        <v>13.82475566864014</v>
       </c>
       <c r="C132" t="n">
         <v>15.35000038146973</v>
@@ -3817,7 +3817,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>11.87938213348389</v>
+        <v>11.87938117980957</v>
       </c>
       <c r="C133" t="n">
         <v>13.1899995803833</v>
@@ -3844,7 +3844,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>14.99558639526367</v>
+        <v>14.99558448791504</v>
       </c>
       <c r="C134" t="n">
         <v>16.64999961853027</v>
@@ -3898,7 +3898,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>12.03249359130859</v>
+        <v>12.03249263763428</v>
       </c>
       <c r="C136" t="n">
         <v>13.35999965667725</v>
@@ -3925,7 +3925,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>11.48310661315918</v>
+        <v>11.4831018447876</v>
       </c>
       <c r="C137" t="n">
         <v>12.75</v>
@@ -3952,7 +3952,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>10.34830284118652</v>
+        <v>10.34830474853516</v>
       </c>
       <c r="C138" t="n">
         <v>11.48999977111816</v>
@@ -3979,7 +3979,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>10.81663513183594</v>
+        <v>10.81663227081299</v>
       </c>
       <c r="C139" t="n">
         <v>12.01000022888184</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>13.3113956451416</v>
+        <v>13.31139469146729</v>
       </c>
       <c r="C141" t="n">
         <v>14.77999973297119</v>
@@ -4137,7 +4137,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>17.0760498046875</v>
+        <v>17.07605171203613</v>
       </c>
       <c r="C145" t="n">
         <v>18.95999908447266</v>
@@ -4162,7 +4162,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>17.56239891052246</v>
+        <v>17.5623950958252</v>
       </c>
       <c r="C146" t="n">
         <v>19.5</v>
@@ -4216,7 +4216,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>15.82417106628418</v>
+        <v>15.82416915893555</v>
       </c>
       <c r="C148" t="n">
         <v>17.56999969482422</v>
@@ -4245,7 +4245,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>13.73686695098877</v>
+        <v>13.73686790466309</v>
       </c>
       <c r="C149" t="n">
         <v>15.21000003814697</v>
@@ -4274,7 +4274,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>15.26318645477295</v>
+        <v>15.26318836212158</v>
       </c>
       <c r="C150" t="n">
         <v>16.89999961853027</v>
@@ -4303,7 +4303,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>15.5883207321167</v>
+        <v>15.58831596374512</v>
       </c>
       <c r="C151" t="n">
         <v>17.26000022888184</v>
@@ -4332,7 +4332,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>14.94484519958496</v>
+        <v>14.94484806060791</v>
       </c>
       <c r="C152" t="n">
         <v>16.5</v>
@@ -4361,7 +4361,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>12.72576332092285</v>
+        <v>12.72576427459717</v>
       </c>
       <c r="C153" t="n">
         <v>14.05000019073486</v>
@@ -4390,7 +4390,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>12.60801792144775</v>
+        <v>12.60801887512207</v>
       </c>
       <c r="C154" t="n">
         <v>13.92000007629395</v>
@@ -4415,7 +4415,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>10.59199810028076</v>
+        <v>10.59199905395508</v>
       </c>
       <c r="C155" t="n">
         <v>11.64999961853027</v>
@@ -4440,7 +4440,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>10.85566234588623</v>
+        <v>10.85566425323486</v>
       </c>
       <c r="C156" t="n">
         <v>11.9399995803833</v>
@@ -4465,7 +4465,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>9.373693466186523</v>
+        <v>9.373691558837891</v>
       </c>
       <c r="C157" t="n">
         <v>10.3100004196167</v>
@@ -4490,7 +4490,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>10.62872123718262</v>
+        <v>10.6287202835083</v>
       </c>
       <c r="C158" t="n">
         <v>11.64000034332275</v>
@@ -4544,7 +4544,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>11.77012252807617</v>
+        <v>11.77012348175049</v>
       </c>
       <c r="C160" t="n">
         <v>12.89000034332275</v>
@@ -4573,7 +4573,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>11.28257846832275</v>
+        <v>11.28258228302002</v>
       </c>
       <c r="C161" t="n">
         <v>12.3100004196167</v>
@@ -4602,7 +4602,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>8.89958381652832</v>
+        <v>8.899580001831055</v>
       </c>
       <c r="C162" t="n">
         <v>9.710000038146973</v>
@@ -4631,7 +4631,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>10.64099884033203</v>
+        <v>10.64100170135498</v>
       </c>
       <c r="C163" t="n">
         <v>11.60999965667725</v>
@@ -4660,7 +4660,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>10.18277645111084</v>
+        <v>10.18277549743652</v>
       </c>
       <c r="C164" t="n">
         <v>11.0600004196167</v>
@@ -4689,7 +4689,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>8.461092948913574</v>
+        <v>8.461091995239258</v>
       </c>
       <c r="C165" t="n">
         <v>9.189999580383301</v>
@@ -4718,7 +4718,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>8.810951232910156</v>
+        <v>8.810955047607422</v>
       </c>
       <c r="C166" t="n">
         <v>9.569999694824219</v>
@@ -4743,7 +4743,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>9.091861724853516</v>
+        <v>9.091863632202148</v>
       </c>
       <c r="C167" t="n">
         <v>9.819999694824219</v>
@@ -4793,7 +4793,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>12.14717197418213</v>
+        <v>12.14717388153076</v>
       </c>
       <c r="C169" t="n">
         <v>13.11999988555908</v>
@@ -4818,7 +4818,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>10.31507110595703</v>
+        <v>10.31507301330566</v>
       </c>
       <c r="C170" t="n">
         <v>11.10000038146973</v>
@@ -4843,7 +4843,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>9.25568675994873</v>
+        <v>9.255683898925781</v>
       </c>
       <c r="C171" t="n">
         <v>9.960000038146973</v>
@@ -4951,7 +4951,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>10.7518367767334</v>
+        <v>10.75183582305908</v>
       </c>
       <c r="C175" t="n">
         <v>11.56999969482422</v>
@@ -4978,7 +4978,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>12.00637340545654</v>
+        <v>12.00637054443359</v>
       </c>
       <c r="C176" t="n">
         <v>12.92000007629395</v>
@@ -5005,7 +5005,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>14.50614929199219</v>
+        <v>14.5061502456665</v>
       </c>
       <c r="C177" t="n">
         <v>15.60999965667725</v>
@@ -5057,7 +5057,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>16.11380958557129</v>
+        <v>16.11381340026855</v>
       </c>
       <c r="C179" t="n">
         <v>17.34000015258789</v>
@@ -5082,7 +5082,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>21.73598861694336</v>
+        <v>21.73599243164062</v>
       </c>
       <c r="C180" t="n">
         <v>23.38999938964844</v>
@@ -5107,7 +5107,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>24.18001556396484</v>
+        <v>24.18001365661621</v>
       </c>
       <c r="C181" t="n">
         <v>26.02000045776367</v>
@@ -5132,7 +5132,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>25.00708198547363</v>
+        <v>25.00707626342773</v>
       </c>
       <c r="C182" t="n">
         <v>26.90999984741211</v>
@@ -5182,7 +5182,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>30.60137367248535</v>
+        <v>30.60138320922852</v>
       </c>
       <c r="C184" t="n">
         <v>32.93000030517578</v>
@@ -5207,7 +5207,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>35.12145614624023</v>
+        <v>35.12145233154297</v>
       </c>
       <c r="C185" t="n">
         <v>37.70999908447266</v>
@@ -5232,7 +5232,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>39.78754806518555</v>
+        <v>39.78755950927734</v>
       </c>
       <c r="C186" t="n">
         <v>42.72000122070312</v>
@@ -5259,7 +5259,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>34.56264495849609</v>
+        <v>34.56264877319336</v>
       </c>
       <c r="C187" t="n">
         <v>37.11000061035156</v>
@@ -5313,7 +5313,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>33.96336364746094</v>
+        <v>33.9633674621582</v>
       </c>
       <c r="C189" t="n">
         <v>36.38999938964844</v>
@@ -5340,7 +5340,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>30.36075782775879</v>
+        <v>30.36075592041016</v>
       </c>
       <c r="C190" t="n">
         <v>32.52999877929688</v>
@@ -5367,7 +5367,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>35.27854156494141</v>
+        <v>35.27853775024414</v>
       </c>
       <c r="C191" t="n">
         <v>37.72000122070312</v>
@@ -5394,7 +5394,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>34.67995834350586</v>
+        <v>34.67995071411133</v>
       </c>
       <c r="C192" t="n">
         <v>37.08000183105469</v>
@@ -5452,7 +5452,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>34.92694091796875</v>
+        <v>34.92692947387695</v>
       </c>
       <c r="C194" t="n">
         <v>37.22000122070312</v>
@@ -5481,7 +5481,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>44.05747985839844</v>
+        <v>44.0574836730957</v>
       </c>
       <c r="C195" t="n">
         <v>46.95000076293945</v>
@@ -5510,7 +5510,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>46.67559432983398</v>
+        <v>46.67559814453125</v>
       </c>
       <c r="C196" t="n">
         <v>49.7400016784668</v>
@@ -5539,7 +5539,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.17107009887695</v>
+        <v>38.17106628417969</v>
       </c>
       <c r="C197" t="n">
         <v>40.54999923706055</v>
@@ -5568,7 +5568,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>36.78730773925781</v>
+        <v>36.78731155395508</v>
       </c>
       <c r="C198" t="n">
         <v>39.08000183105469</v>
@@ -5597,7 +5597,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54341125488281</v>
+        <v>27.54341316223145</v>
       </c>
       <c r="C199" t="n">
         <v>29.26000022888184</v>
@@ -5626,7 +5626,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>29.86851119995117</v>
+        <v>29.86851692199707</v>
       </c>
       <c r="C200" t="n">
         <v>31.54999923706055</v>
@@ -5655,7 +5655,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>28.02243995666504</v>
+        <v>28.0224437713623</v>
       </c>
       <c r="C201" t="n">
         <v>29.60000038146973</v>
@@ -5684,7 +5684,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>25.87342643737793</v>
+        <v>25.8734245300293</v>
       </c>
       <c r="C202" t="n">
         <v>27.32999992370605</v>
@@ -5742,7 +5742,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>37.87581253051758</v>
+        <v>37.87582015991211</v>
       </c>
       <c r="C204" t="n">
         <v>39.79999923706055</v>
@@ -5771,7 +5771,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.162841796875</v>
+        <v>36.16283798217773</v>
       </c>
       <c r="C205" t="n">
         <v>38</v>
@@ -5829,7 +5829,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.11872863769531</v>
+        <v>39.11873626708984</v>
       </c>
       <c r="C207" t="n">
         <v>40.97000122070312</v>
@@ -5858,7 +5858,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>39.06143569946289</v>
+        <v>39.06144332885742</v>
       </c>
       <c r="C208" t="n">
         <v>40.90999984741211</v>
@@ -5887,7 +5887,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>36.32951354980469</v>
+        <v>36.32952117919922</v>
       </c>
       <c r="C209" t="n">
         <v>37.90999984741211</v>
@@ -5916,7 +5916,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>32.90835952758789</v>
+        <v>32.90835189819336</v>
       </c>
       <c r="C210" t="n">
         <v>34.34000015258789</v>
@@ -5945,7 +5945,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>38.3323860168457</v>
+        <v>38.33238983154297</v>
       </c>
       <c r="C211" t="n">
         <v>40</v>
@@ -6003,7 +6003,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>38.38755416870117</v>
+        <v>38.38755035400391</v>
       </c>
       <c r="C213" t="n">
         <v>39.90999984741211</v>
@@ -6032,7 +6032,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>35.86749649047852</v>
+        <v>35.86750030517578</v>
       </c>
       <c r="C214" t="n">
         <v>37.29000091552734</v>
@@ -6061,7 +6061,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>32.62311935424805</v>
+        <v>32.62310791015625</v>
       </c>
       <c r="C215" t="n">
         <v>33.77999877929688</v>
@@ -6090,7 +6090,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>36.04187774658203</v>
+        <v>36.04187393188477</v>
       </c>
       <c r="C216" t="n">
         <v>37.31999969482422</v>
@@ -6119,7 +6119,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>41.1120719909668</v>
+        <v>41.11207962036133</v>
       </c>
       <c r="C217" t="n">
         <v>42.56999969482422</v>
@@ -6148,7 +6148,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>38.47043228149414</v>
+        <v>38.47042846679688</v>
       </c>
       <c r="C218" t="n">
         <v>39.68999862670898</v>
@@ -6177,7 +6177,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>36.64818954467773</v>
+        <v>36.64819717407227</v>
       </c>
       <c r="C219" t="n">
         <v>37.81000137329102</v>
@@ -6235,7 +6235,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>48.54899597167969</v>
+        <v>48.54900360107422</v>
       </c>
       <c r="C221" t="n">
         <v>49.93999862670898</v>
@@ -6264,7 +6264,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>51.26128768920898</v>
+        <v>51.26128387451172</v>
       </c>
       <c r="C222" t="n">
         <v>52.72999954223633</v>
@@ -6322,7 +6322,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>44.27468490600586</v>
+        <v>44.27468872070312</v>
       </c>
       <c r="C224" t="n">
         <v>45.40999984741211</v>
@@ -6351,7 +6351,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>43.17293930053711</v>
+        <v>43.17293548583984</v>
       </c>
       <c r="C225" t="n">
         <v>44.27999877929688</v>
@@ -6409,7 +6409,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>44.02960205078125</v>
+        <v>44.02960968017578</v>
       </c>
       <c r="C227" t="n">
         <v>45.02000045776367</v>
@@ -6438,7 +6438,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>43.22765350341797</v>
+        <v>43.2276496887207</v>
       </c>
       <c r="C228" t="n">
         <v>44.20000076293945</v>
@@ -6467,7 +6467,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>37.24228286743164</v>
+        <v>37.24228668212891</v>
       </c>
       <c r="C229" t="n">
         <v>38.08000183105469</v>
@@ -6525,7 +6525,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>36.23562240600586</v>
+        <v>36.23561859130859</v>
       </c>
       <c r="C231" t="n">
         <v>36.90999984741211</v>
@@ -6583,7 +6583,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>35.52960205078125</v>
+        <v>35.52960586547852</v>
       </c>
       <c r="C233" t="n">
         <v>36.02999877929688</v>
@@ -6699,7 +6699,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>43.92777633666992</v>
+        <v>43.92777252197266</v>
       </c>
       <c r="C237" t="n">
         <v>44.40000152587891</v>
